--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB2BB163-33AF-4676-B469-0D38CC495160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70DC1B8-B5E7-44A8-8FFA-18916702904B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -445,9 +445,6 @@
     <t>Frooti Big Bottel Cold Drink</t>
   </si>
   <si>
-    <t>Water Bottle 30</t>
-  </si>
-  <si>
     <t>Water Bottle 20</t>
   </si>
   <si>
@@ -608,6 +605,9 @@
   </si>
   <si>
     <t>Big Glass Single</t>
+  </si>
+  <si>
+    <t>Water Bottle 35</t>
   </si>
 </sst>
 </file>
@@ -1015,7 +1015,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1055,7 +1055,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1075,7 +1075,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1095,7 +1095,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1115,7 +1115,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7">
         <v>40</v>
@@ -1124,7 +1124,7 @@
         <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F7" t="s">
         <v>6</v>
@@ -1135,7 +1135,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C8">
         <v>50</v>
@@ -1144,7 +1144,7 @@
         <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F8" t="s">
         <v>6</v>
@@ -1155,7 +1155,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C9">
         <v>20</v>
@@ -1164,7 +1164,7 @@
         <v>30</v>
       </c>
       <c r="E9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F9" t="s">
         <v>6</v>
@@ -1175,7 +1175,7 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C10">
         <v>40</v>
@@ -1184,7 +1184,7 @@
         <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F10" t="s">
         <v>6</v>
@@ -1195,7 +1195,7 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C11">
         <v>60</v>
@@ -1204,7 +1204,7 @@
         <v>100</v>
       </c>
       <c r="E11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F11" t="s">
         <v>6</v>
@@ -1215,7 +1215,7 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C12">
         <v>40</v>
@@ -1224,7 +1224,7 @@
         <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F12" t="s">
         <v>6</v>
@@ -1235,7 +1235,7 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C13">
         <v>50</v>
@@ -1244,7 +1244,7 @@
         <v>100</v>
       </c>
       <c r="E13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F13" t="s">
         <v>6</v>
@@ -1255,7 +1255,7 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C14">
         <v>40</v>
@@ -1264,7 +1264,7 @@
         <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F14" t="s">
         <v>6</v>
@@ -1275,7 +1275,7 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C15">
         <v>80</v>
@@ -1284,7 +1284,7 @@
         <v>160</v>
       </c>
       <c r="E15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F15" t="s">
         <v>6</v>
@@ -1295,7 +1295,7 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C16">
         <v>90</v>
@@ -1304,7 +1304,7 @@
         <v>175</v>
       </c>
       <c r="E16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F16" t="s">
         <v>6</v>
@@ -1315,7 +1315,7 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1324,7 +1324,7 @@
         <v>120</v>
       </c>
       <c r="E17" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F17" t="s">
         <v>6</v>
@@ -2115,7 +2115,7 @@
         <v>100</v>
       </c>
       <c r="B57" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>15</v>
       </c>
       <c r="E57" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F57" t="s">
         <v>6</v>
@@ -2335,7 +2335,7 @@
         <v>100</v>
       </c>
       <c r="B68" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -2344,7 +2344,7 @@
         <v>50</v>
       </c>
       <c r="E68" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F68" t="s">
         <v>6</v>
@@ -2395,7 +2395,7 @@
         <v>98</v>
       </c>
       <c r="B71" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -2404,7 +2404,7 @@
         <v>10</v>
       </c>
       <c r="E71" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F71" t="s">
         <v>6</v>
@@ -2475,7 +2475,7 @@
         <v>98</v>
       </c>
       <c r="B75" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2484,7 +2484,7 @@
         <v>10</v>
       </c>
       <c r="E75" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F75" t="s">
         <v>6</v>
@@ -2535,7 +2535,7 @@
         <v>98</v>
       </c>
       <c r="B78" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>20</v>
       </c>
       <c r="E78" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F78" t="s">
         <v>6</v>
@@ -2635,7 +2635,7 @@
         <v>98</v>
       </c>
       <c r="B83" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2675,7 +2675,7 @@
         <v>98</v>
       </c>
       <c r="B85" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2715,7 +2715,7 @@
         <v>98</v>
       </c>
       <c r="B87" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2724,7 +2724,7 @@
         <v>60</v>
       </c>
       <c r="E87" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F87" t="s">
         <v>6</v>
@@ -2735,7 +2735,7 @@
         <v>98</v>
       </c>
       <c r="B88" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2744,7 +2744,7 @@
         <v>125</v>
       </c>
       <c r="E88" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F88" t="s">
         <v>6</v>
@@ -2795,7 +2795,7 @@
         <v>98</v>
       </c>
       <c r="B91" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2804,7 +2804,7 @@
         <v>40</v>
       </c>
       <c r="E91" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F91" t="s">
         <v>6</v>
@@ -2815,7 +2815,7 @@
         <v>98</v>
       </c>
       <c r="B92" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2824,7 +2824,7 @@
         <v>50</v>
       </c>
       <c r="E92" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F92" t="s">
         <v>6</v>
@@ -2864,7 +2864,7 @@
         <v>100</v>
       </c>
       <c r="E94" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F94" t="s">
         <v>6</v>
@@ -2875,7 +2875,7 @@
         <v>98</v>
       </c>
       <c r="B95" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -2884,7 +2884,7 @@
         <v>100</v>
       </c>
       <c r="E95" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F95" t="s">
         <v>6</v>
@@ -2895,7 +2895,7 @@
         <v>98</v>
       </c>
       <c r="B96" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -2904,7 +2904,7 @@
         <v>20</v>
       </c>
       <c r="E96" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F96" t="s">
         <v>6</v>
@@ -2915,16 +2915,16 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>140</v>
+        <v>194</v>
       </c>
       <c r="C97">
         <v>0</v>
       </c>
       <c r="D97">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E97" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F97" t="s">
         <v>6</v>
@@ -2935,7 +2935,7 @@
         <v>98</v>
       </c>
       <c r="B98" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C98">
         <v>5</v>
@@ -2944,7 +2944,7 @@
         <v>10</v>
       </c>
       <c r="E98" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F98" t="s">
         <v>6</v>
@@ -2955,7 +2955,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -2964,7 +2964,7 @@
         <v>40</v>
       </c>
       <c r="E99" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F99" t="s">
         <v>6</v>
@@ -2975,7 +2975,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -2984,7 +2984,7 @@
         <v>1</v>
       </c>
       <c r="E100" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F100" t="s">
         <v>6</v>
@@ -2995,7 +2995,7 @@
         <v>98</v>
       </c>
       <c r="B101" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C101">
         <v>3</v>
@@ -3004,7 +3004,7 @@
         <v>5</v>
       </c>
       <c r="E101" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F101" t="s">
         <v>6</v>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70DC1B8-B5E7-44A8-8FFA-18916702904B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FDFCE55-10AE-4DB5-82CC-D12AEBC5658D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$81</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="202">
   <si>
     <t>Item</t>
   </si>
@@ -304,9 +304,6 @@
     <t>Dite Coke 25 rs.jpg</t>
   </si>
   <si>
-    <t>Thums up 35</t>
-  </si>
-  <si>
     <t>Thums up 35.jpg</t>
   </si>
   <si>
@@ -559,9 +556,6 @@
     <t>RedBull.jpg</t>
   </si>
   <si>
-    <t>Thumsup Can 40 rs</t>
-  </si>
-  <si>
     <t>Glass</t>
   </si>
   <si>
@@ -608,6 +602,33 @@
   </si>
   <si>
     <t>Water Bottle 35</t>
+  </si>
+  <si>
+    <t>Gol Gappe 20</t>
+  </si>
+  <si>
+    <t>Samosa 10</t>
+  </si>
+  <si>
+    <t>Kachori</t>
+  </si>
+  <si>
+    <t>Samosa.jpg</t>
+  </si>
+  <si>
+    <t>Aloo Puri.jpg</t>
+  </si>
+  <si>
+    <t>Gol Gappe.jpg</t>
+  </si>
+  <si>
+    <t>Water Bottle 30</t>
+  </si>
+  <si>
+    <t>Thumsup/Sprit/Coca Cola Can 40 rs</t>
+  </si>
+  <si>
+    <t>Thums up Bottel 40</t>
   </si>
 </sst>
 </file>
@@ -980,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -1015,7 +1036,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1035,7 +1056,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1055,7 +1076,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1075,7 +1096,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1095,7 +1116,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1115,7 +1136,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C7">
         <v>40</v>
@@ -1124,7 +1145,7 @@
         <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F7" t="s">
         <v>6</v>
@@ -1135,7 +1156,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C8">
         <v>50</v>
@@ -1144,7 +1165,7 @@
         <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F8" t="s">
         <v>6</v>
@@ -1155,7 +1176,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C9">
         <v>20</v>
@@ -1164,7 +1185,7 @@
         <v>30</v>
       </c>
       <c r="E9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F9" t="s">
         <v>6</v>
@@ -1175,7 +1196,7 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C10">
         <v>40</v>
@@ -1184,7 +1205,7 @@
         <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F10" t="s">
         <v>6</v>
@@ -1195,7 +1216,7 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C11">
         <v>60</v>
@@ -1204,7 +1225,7 @@
         <v>100</v>
       </c>
       <c r="E11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F11" t="s">
         <v>6</v>
@@ -1215,7 +1236,7 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C12">
         <v>40</v>
@@ -1224,7 +1245,7 @@
         <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F12" t="s">
         <v>6</v>
@@ -1235,7 +1256,7 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C13">
         <v>50</v>
@@ -1244,7 +1265,7 @@
         <v>100</v>
       </c>
       <c r="E13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F13" t="s">
         <v>6</v>
@@ -1255,7 +1276,7 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C14">
         <v>40</v>
@@ -1264,7 +1285,7 @@
         <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F14" t="s">
         <v>6</v>
@@ -1275,7 +1296,7 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C15">
         <v>80</v>
@@ -1284,7 +1305,7 @@
         <v>160</v>
       </c>
       <c r="E15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F15" t="s">
         <v>6</v>
@@ -1295,7 +1316,7 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C16">
         <v>90</v>
@@ -1304,7 +1325,7 @@
         <v>175</v>
       </c>
       <c r="E16" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F16" t="s">
         <v>6</v>
@@ -1315,7 +1336,7 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1324,7 +1345,7 @@
         <v>120</v>
       </c>
       <c r="E17" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F17" t="s">
         <v>6</v>
@@ -1672,7 +1693,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B35" t="s">
         <v>43</v>
@@ -1692,7 +1713,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B36" t="s">
         <v>45</v>
@@ -1712,7 +1733,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B37" t="s">
         <v>47</v>
@@ -1732,7 +1753,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B38" t="s">
         <v>49</v>
@@ -1752,7 +1773,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B39" t="s">
         <v>51</v>
@@ -1772,7 +1793,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B40" t="s">
         <v>53</v>
@@ -1792,7 +1813,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B41" t="s">
         <v>54</v>
@@ -1812,7 +1833,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B42" t="s">
         <v>55</v>
@@ -1832,19 +1853,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>193</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E43" t="s">
-        <v>57</v>
+        <v>198</v>
       </c>
       <c r="F43" t="s">
         <v>6</v>
@@ -1852,10 +1873,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>194</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -1864,7 +1885,7 @@
         <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>59</v>
+        <v>196</v>
       </c>
       <c r="F44" t="s">
         <v>6</v>
@@ -1872,19 +1893,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>60</v>
+        <v>195</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E45" t="s">
-        <v>61</v>
+        <v>197</v>
       </c>
       <c r="F45" t="s">
         <v>6</v>
@@ -1892,10 +1913,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B46" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -1904,7 +1925,7 @@
         <v>5</v>
       </c>
       <c r="E46" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F46" t="s">
         <v>6</v>
@@ -1912,10 +1933,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B47" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -1924,7 +1945,7 @@
         <v>10</v>
       </c>
       <c r="E47" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F47" t="s">
         <v>6</v>
@@ -1932,19 +1953,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B48" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C48">
         <v>0</v>
       </c>
       <c r="D48">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E48" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F48" t="s">
         <v>6</v>
@@ -1952,19 +1973,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B49" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E49" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F49" t="s">
         <v>6</v>
@@ -1972,10 +1993,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B50" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -1984,7 +2005,7 @@
         <v>10</v>
       </c>
       <c r="E50" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F50" t="s">
         <v>6</v>
@@ -1992,19 +2013,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B51" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E51" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F51" t="s">
         <v>6</v>
@@ -2012,19 +2033,19 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B52" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E52" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F52" t="s">
         <v>6</v>
@@ -2032,19 +2053,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B53" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E53" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F53" t="s">
         <v>6</v>
@@ -2052,19 +2073,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B54" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="C54">
         <v>0</v>
       </c>
       <c r="D54">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E54" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="F54" t="s">
         <v>6</v>
@@ -2072,19 +2093,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B55" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E55" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F55" t="s">
         <v>6</v>
@@ -2092,19 +2113,19 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B56" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E56" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F56" t="s">
         <v>6</v>
@@ -2112,19 +2133,19 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B57" t="s">
-        <v>190</v>
+        <v>114</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E57" t="s">
-        <v>191</v>
+        <v>116</v>
       </c>
       <c r="F57" t="s">
         <v>6</v>
@@ -2132,19 +2153,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B58" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="E58" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="F58" t="s">
         <v>6</v>
@@ -2152,19 +2173,19 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B59" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="E59" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="F59" t="s">
         <v>6</v>
@@ -2172,19 +2193,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B60" t="s">
-        <v>109</v>
+        <v>188</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="E60" t="s">
-        <v>110</v>
+        <v>189</v>
       </c>
       <c r="F60" t="s">
         <v>6</v>
@@ -2192,19 +2213,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B61" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E61" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="F61" t="s">
         <v>6</v>
@@ -2212,19 +2233,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B62" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E62" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="F62" t="s">
         <v>6</v>
@@ -2232,19 +2253,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B63" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="E63" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="F63" t="s">
         <v>6</v>
@@ -2252,19 +2273,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B64" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E64" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="F64" t="s">
         <v>6</v>
@@ -2272,19 +2293,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B65" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="E65" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="F65" t="s">
         <v>6</v>
@@ -2292,7 +2313,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B66" t="s">
         <v>131</v>
@@ -2301,10 +2322,10 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E66" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F66" t="s">
         <v>6</v>
@@ -2312,19 +2333,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B67" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E67" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="F67" t="s">
         <v>6</v>
@@ -2332,19 +2353,19 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B68" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
       <c r="D68">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E68" t="s">
-        <v>175</v>
+        <v>136</v>
       </c>
       <c r="F68" t="s">
         <v>6</v>
@@ -2352,19 +2373,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B69" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E69" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="F69" t="s">
         <v>6</v>
@@ -2372,19 +2393,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B70" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E70" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F70" t="s">
         <v>6</v>
@@ -2392,19 +2413,19 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B71" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E71" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="F71" t="s">
         <v>6</v>
@@ -2412,10 +2433,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B72" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2424,7 +2445,7 @@
         <v>10</v>
       </c>
       <c r="E72" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="F72" t="s">
         <v>6</v>
@@ -2432,19 +2453,19 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B73" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E73" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="F73" t="s">
         <v>6</v>
@@ -2452,10 +2473,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B74" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2464,7 +2485,7 @@
         <v>10</v>
       </c>
       <c r="E74" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F74" t="s">
         <v>6</v>
@@ -2472,10 +2493,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B75" t="s">
-        <v>172</v>
+        <v>83</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2484,7 +2505,7 @@
         <v>10</v>
       </c>
       <c r="E75" t="s">
-        <v>173</v>
+        <v>84</v>
       </c>
       <c r="F75" t="s">
         <v>6</v>
@@ -2492,19 +2513,19 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B76" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E76" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F76" t="s">
         <v>6</v>
@@ -2512,19 +2533,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B77" t="s">
-        <v>89</v>
+        <v>171</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E77" t="s">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="F77" t="s">
         <v>6</v>
@@ -2532,10 +2553,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B78" t="s">
-        <v>185</v>
+        <v>87</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2544,7 +2565,7 @@
         <v>20</v>
       </c>
       <c r="E78" t="s">
-        <v>186</v>
+        <v>88</v>
       </c>
       <c r="F78" t="s">
         <v>6</v>
@@ -2552,10 +2573,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B79" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2564,7 +2585,7 @@
         <v>20</v>
       </c>
       <c r="E79" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F79" t="s">
         <v>6</v>
@@ -2572,10 +2593,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B80" t="s">
-        <v>101</v>
+        <v>183</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2584,7 +2605,7 @@
         <v>20</v>
       </c>
       <c r="E80" t="s">
-        <v>103</v>
+        <v>184</v>
       </c>
       <c r="F80" t="s">
         <v>6</v>
@@ -2592,10 +2613,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B81" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2604,7 +2625,7 @@
         <v>20</v>
       </c>
       <c r="E81" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F81" t="s">
         <v>6</v>
@@ -2612,10 +2633,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B82" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2624,7 +2645,7 @@
         <v>20</v>
       </c>
       <c r="E82" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="F82" t="s">
         <v>6</v>
@@ -2632,19 +2653,19 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>153</v>
+        <v>101</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E83" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="F83" t="s">
         <v>6</v>
@@ -2652,19 +2673,19 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B84" t="s">
-        <v>178</v>
+        <v>121</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E84" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="F84" t="s">
         <v>6</v>
@@ -2672,19 +2693,19 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B85" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E85" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F85" t="s">
         <v>6</v>
@@ -2692,19 +2713,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B86" t="s">
-        <v>126</v>
+        <v>200</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E86" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="F86" t="s">
         <v>6</v>
@@ -2712,19 +2733,19 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B87" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="C87">
         <v>0</v>
       </c>
       <c r="D87">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E87" t="s">
-        <v>174</v>
+        <v>94</v>
       </c>
       <c r="F87" t="s">
         <v>6</v>
@@ -2732,19 +2753,19 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B88" t="s">
-        <v>176</v>
+        <v>125</v>
       </c>
       <c r="C88">
         <v>0</v>
       </c>
       <c r="D88">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="E88" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="F88" t="s">
         <v>6</v>
@@ -2752,19 +2773,19 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B89" t="s">
-        <v>93</v>
+        <v>169</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="E89" t="s">
-        <v>94</v>
+        <v>173</v>
       </c>
       <c r="F89" t="s">
         <v>6</v>
@@ -2772,19 +2793,19 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B90" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="E90" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="F90" t="s">
         <v>6</v>
@@ -2792,10 +2813,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B91" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2804,7 +2825,7 @@
         <v>40</v>
       </c>
       <c r="E91" t="s">
-        <v>186</v>
+        <v>93</v>
       </c>
       <c r="F91" t="s">
         <v>6</v>
@@ -2812,10 +2833,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2824,7 +2845,7 @@
         <v>50</v>
       </c>
       <c r="E92" t="s">
-        <v>186</v>
+        <v>128</v>
       </c>
       <c r="F92" t="s">
         <v>6</v>
@@ -2832,19 +2853,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B93" t="s">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="E93" t="s">
-        <v>129</v>
+        <v>184</v>
       </c>
       <c r="F93" t="s">
         <v>6</v>
@@ -2852,19 +2873,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B94" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="C94">
         <v>0</v>
       </c>
       <c r="D94">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E94" t="s">
-        <v>142</v>
+        <v>184</v>
       </c>
       <c r="F94" t="s">
         <v>6</v>
@@ -2872,19 +2893,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B95" t="s">
-        <v>184</v>
+        <v>127</v>
       </c>
       <c r="C95">
         <v>0</v>
       </c>
       <c r="D95">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E95" t="s">
-        <v>186</v>
+        <v>128</v>
       </c>
       <c r="F95" t="s">
         <v>6</v>
@@ -2892,16 +2913,16 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C96">
         <v>0</v>
       </c>
       <c r="D96">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E96" t="s">
         <v>141</v>
@@ -2912,19 +2933,19 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B97" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="C97">
         <v>0</v>
       </c>
       <c r="D97">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="E97" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="F97" t="s">
         <v>6</v>
@@ -2932,19 +2953,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C98">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>10</v>
       </c>
       <c r="E98" t="s">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="F98" t="s">
         <v>6</v>
@@ -2952,19 +2973,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>181</v>
+        <v>139</v>
       </c>
       <c r="C99">
         <v>0</v>
       </c>
       <c r="D99">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E99" t="s">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="F99" t="s">
         <v>6</v>
@@ -2972,19 +2993,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B100" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C100">
         <v>0</v>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E100" t="s">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="F100" t="s">
         <v>6</v>
@@ -2992,21 +3013,101 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B101" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101">
+        <v>35</v>
+      </c>
+      <c r="E101" t="s">
+        <v>140</v>
+      </c>
+      <c r="F101" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>97</v>
+      </c>
+      <c r="B102" t="s">
+        <v>177</v>
+      </c>
+      <c r="C102">
+        <v>5</v>
+      </c>
+      <c r="D102">
+        <v>10</v>
+      </c>
+      <c r="E102" t="s">
+        <v>178</v>
+      </c>
+      <c r="F102" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>97</v>
+      </c>
+      <c r="B103" t="s">
+        <v>179</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+      <c r="D103">
+        <v>40</v>
+      </c>
+      <c r="E103" t="s">
+        <v>178</v>
+      </c>
+      <c r="F103" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>97</v>
+      </c>
+      <c r="B104" t="s">
+        <v>190</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+      <c r="D104">
+        <v>1</v>
+      </c>
+      <c r="E104" t="s">
+        <v>178</v>
+      </c>
+      <c r="F104" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>97</v>
+      </c>
+      <c r="B105" t="s">
+        <v>191</v>
+      </c>
+      <c r="C105">
         <v>3</v>
       </c>
-      <c r="D101">
+      <c r="D105">
         <v>5</v>
       </c>
-      <c r="E101" t="s">
-        <v>180</v>
-      </c>
-      <c r="F101" t="s">
+      <c r="E105" t="s">
+        <v>178</v>
+      </c>
+      <c r="F105" t="s">
         <v>6</v>
       </c>
     </row>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FDFCE55-10AE-4DB5-82CC-D12AEBC5658D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE2F19F-A4D6-41C6-8A63-EA535F8F3EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="206">
   <si>
     <t>Item</t>
   </si>
@@ -629,6 +629,18 @@
   </si>
   <si>
     <t>Thums up Bottel 40</t>
+  </si>
+  <si>
+    <t>Tea 15</t>
+  </si>
+  <si>
+    <t>Tea.jpg</t>
+  </si>
+  <si>
+    <t>Aloo Pakodi</t>
+  </si>
+  <si>
+    <t>Aloo Pakodi.jpg</t>
   </si>
 </sst>
 </file>
@@ -1001,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -1916,16 +1928,16 @@
         <v>99</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>204</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E46" t="s">
-        <v>57</v>
+        <v>205</v>
       </c>
       <c r="F46" t="s">
         <v>6</v>
@@ -1936,16 +1948,16 @@
         <v>99</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E47" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F47" t="s">
         <v>6</v>
@@ -1956,16 +1968,16 @@
         <v>99</v>
       </c>
       <c r="B48" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C48">
         <v>0</v>
       </c>
       <c r="D48">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E48" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F48" t="s">
         <v>6</v>
@@ -1976,16 +1988,16 @@
         <v>99</v>
       </c>
       <c r="B49" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E49" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F49" t="s">
         <v>6</v>
@@ -1996,16 +2008,16 @@
         <v>99</v>
       </c>
       <c r="B50" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C50">
         <v>0</v>
       </c>
       <c r="D50">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E50" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F50" t="s">
         <v>6</v>
@@ -2016,16 +2028,16 @@
         <v>99</v>
       </c>
       <c r="B51" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E51" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F51" t="s">
         <v>6</v>
@@ -2036,16 +2048,16 @@
         <v>99</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E52" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F52" t="s">
         <v>6</v>
@@ -2056,7 +2068,7 @@
         <v>99</v>
       </c>
       <c r="B53" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -2065,7 +2077,7 @@
         <v>10</v>
       </c>
       <c r="E53" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F53" t="s">
         <v>6</v>
@@ -2076,16 +2088,16 @@
         <v>99</v>
       </c>
       <c r="B54" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C54">
         <v>0</v>
       </c>
       <c r="D54">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E54" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F54" t="s">
         <v>6</v>
@@ -2096,16 +2108,16 @@
         <v>99</v>
       </c>
       <c r="B55" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E55" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F55" t="s">
         <v>6</v>
@@ -2116,16 +2128,16 @@
         <v>99</v>
       </c>
       <c r="B56" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E56" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F56" t="s">
         <v>6</v>
@@ -2136,16 +2148,16 @@
         <v>99</v>
       </c>
       <c r="B57" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="E57" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="F57" t="s">
         <v>6</v>
@@ -2156,16 +2168,16 @@
         <v>99</v>
       </c>
       <c r="B58" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="E58" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="F58" t="s">
         <v>6</v>
@@ -2176,16 +2188,16 @@
         <v>99</v>
       </c>
       <c r="B59" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E59" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F59" t="s">
         <v>6</v>
@@ -2196,16 +2208,16 @@
         <v>99</v>
       </c>
       <c r="B60" t="s">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E60" t="s">
-        <v>189</v>
+        <v>80</v>
       </c>
       <c r="F60" t="s">
         <v>6</v>
@@ -2216,16 +2228,16 @@
         <v>99</v>
       </c>
       <c r="B61" t="s">
-        <v>105</v>
+        <v>188</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="E61" t="s">
-        <v>104</v>
+        <v>189</v>
       </c>
       <c r="F61" t="s">
         <v>6</v>
@@ -2236,16 +2248,16 @@
         <v>99</v>
       </c>
       <c r="B62" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E62" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F62" t="s">
         <v>6</v>
@@ -2256,16 +2268,16 @@
         <v>99</v>
       </c>
       <c r="B63" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E63" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F63" t="s">
         <v>6</v>
@@ -2276,7 +2288,7 @@
         <v>99</v>
       </c>
       <c r="B64" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -2285,7 +2297,7 @@
         <v>52</v>
       </c>
       <c r="E64" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F64" t="s">
         <v>6</v>
@@ -2296,16 +2308,16 @@
         <v>99</v>
       </c>
       <c r="B65" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E65" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F65" t="s">
         <v>6</v>
@@ -2316,16 +2328,16 @@
         <v>99</v>
       </c>
       <c r="B66" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E66" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="F66" t="s">
         <v>6</v>
@@ -2336,16 +2348,16 @@
         <v>99</v>
       </c>
       <c r="B67" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E67" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F67" t="s">
         <v>6</v>
@@ -2356,7 +2368,7 @@
         <v>99</v>
       </c>
       <c r="B68" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -2365,7 +2377,7 @@
         <v>10</v>
       </c>
       <c r="E68" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F68" t="s">
         <v>6</v>
@@ -2376,16 +2388,16 @@
         <v>99</v>
       </c>
       <c r="B69" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E69" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F69" t="s">
         <v>6</v>
@@ -2396,16 +2408,16 @@
         <v>99</v>
       </c>
       <c r="B70" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E70" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="F70" t="s">
         <v>6</v>
@@ -2416,16 +2428,16 @@
         <v>99</v>
       </c>
       <c r="B71" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E71" t="s">
-        <v>174</v>
+        <v>120</v>
       </c>
       <c r="F71" t="s">
         <v>6</v>
@@ -2436,16 +2448,16 @@
         <v>99</v>
       </c>
       <c r="B72" t="s">
-        <v>123</v>
+        <v>170</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E72" t="s">
-        <v>124</v>
+        <v>174</v>
       </c>
       <c r="F72" t="s">
         <v>6</v>
@@ -2456,16 +2468,16 @@
         <v>99</v>
       </c>
       <c r="B73" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E73" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="F73" t="s">
         <v>6</v>
@@ -2473,19 +2485,19 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B74" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="F74" t="s">
         <v>6</v>
@@ -2496,16 +2508,16 @@
         <v>97</v>
       </c>
       <c r="B75" t="s">
-        <v>83</v>
+        <v>202</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E75" t="s">
-        <v>84</v>
+        <v>203</v>
       </c>
       <c r="F75" t="s">
         <v>6</v>
@@ -2516,7 +2528,7 @@
         <v>97</v>
       </c>
       <c r="B76" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2525,7 +2537,7 @@
         <v>10</v>
       </c>
       <c r="E76" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F76" t="s">
         <v>6</v>
@@ -2536,7 +2548,7 @@
         <v>97</v>
       </c>
       <c r="B77" t="s">
-        <v>171</v>
+        <v>83</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2545,7 +2557,7 @@
         <v>10</v>
       </c>
       <c r="E77" t="s">
-        <v>172</v>
+        <v>84</v>
       </c>
       <c r="F77" t="s">
         <v>6</v>
@@ -2556,16 +2568,16 @@
         <v>97</v>
       </c>
       <c r="B78" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E78" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F78" t="s">
         <v>6</v>
@@ -2576,16 +2588,16 @@
         <v>97</v>
       </c>
       <c r="B79" t="s">
-        <v>89</v>
+        <v>171</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E79" t="s">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="F79" t="s">
         <v>6</v>
@@ -2596,7 +2608,7 @@
         <v>97</v>
       </c>
       <c r="B80" t="s">
-        <v>183</v>
+        <v>87</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2605,7 +2617,7 @@
         <v>20</v>
       </c>
       <c r="E80" t="s">
-        <v>184</v>
+        <v>88</v>
       </c>
       <c r="F80" t="s">
         <v>6</v>
@@ -2616,7 +2628,7 @@
         <v>97</v>
       </c>
       <c r="B81" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2625,7 +2637,7 @@
         <v>20</v>
       </c>
       <c r="E81" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F81" t="s">
         <v>6</v>
@@ -2636,7 +2648,7 @@
         <v>97</v>
       </c>
       <c r="B82" t="s">
-        <v>100</v>
+        <v>183</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2645,7 +2657,7 @@
         <v>20</v>
       </c>
       <c r="E82" t="s">
-        <v>102</v>
+        <v>184</v>
       </c>
       <c r="F82" t="s">
         <v>6</v>
@@ -2656,7 +2668,7 @@
         <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2665,7 +2677,7 @@
         <v>20</v>
       </c>
       <c r="E83" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F83" t="s">
         <v>6</v>
@@ -2676,7 +2688,7 @@
         <v>97</v>
       </c>
       <c r="B84" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2685,7 +2697,7 @@
         <v>20</v>
       </c>
       <c r="E84" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="F84" t="s">
         <v>6</v>
@@ -2696,16 +2708,16 @@
         <v>97</v>
       </c>
       <c r="B85" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E85" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="F85" t="s">
         <v>6</v>
@@ -2716,16 +2728,16 @@
         <v>97</v>
       </c>
       <c r="B86" t="s">
-        <v>200</v>
+        <v>121</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E86" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="F86" t="s">
         <v>6</v>
@@ -2736,16 +2748,16 @@
         <v>97</v>
       </c>
       <c r="B87" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C87">
         <v>0</v>
       </c>
       <c r="D87">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E87" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F87" t="s">
         <v>6</v>
@@ -2756,16 +2768,16 @@
         <v>97</v>
       </c>
       <c r="B88" t="s">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="C88">
         <v>0</v>
       </c>
       <c r="D88">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E88" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="F88" t="s">
         <v>6</v>
@@ -2776,16 +2788,16 @@
         <v>97</v>
       </c>
       <c r="B89" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E89" t="s">
-        <v>173</v>
+        <v>94</v>
       </c>
       <c r="F89" t="s">
         <v>6</v>
@@ -2796,16 +2808,16 @@
         <v>97</v>
       </c>
       <c r="B90" t="s">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="E90" t="s">
-        <v>176</v>
+        <v>126</v>
       </c>
       <c r="F90" t="s">
         <v>6</v>
@@ -2816,16 +2828,16 @@
         <v>97</v>
       </c>
       <c r="B91" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="C91">
         <v>0</v>
       </c>
       <c r="D91">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E91" t="s">
-        <v>93</v>
+        <v>173</v>
       </c>
       <c r="F91" t="s">
         <v>6</v>
@@ -2836,16 +2848,16 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="C92">
         <v>0</v>
       </c>
       <c r="D92">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="E92" t="s">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="F92" t="s">
         <v>6</v>
@@ -2856,7 +2868,7 @@
         <v>97</v>
       </c>
       <c r="B93" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2865,7 +2877,7 @@
         <v>40</v>
       </c>
       <c r="E93" t="s">
-        <v>184</v>
+        <v>93</v>
       </c>
       <c r="F93" t="s">
         <v>6</v>
@@ -2876,7 +2888,7 @@
         <v>97</v>
       </c>
       <c r="B94" t="s">
-        <v>181</v>
+        <v>137</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2885,7 +2897,7 @@
         <v>50</v>
       </c>
       <c r="E94" t="s">
-        <v>184</v>
+        <v>128</v>
       </c>
       <c r="F94" t="s">
         <v>6</v>
@@ -2896,16 +2908,16 @@
         <v>97</v>
       </c>
       <c r="B95" t="s">
-        <v>127</v>
+        <v>180</v>
       </c>
       <c r="C95">
         <v>0</v>
       </c>
       <c r="D95">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="E95" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="F95" t="s">
         <v>6</v>
@@ -2916,16 +2928,16 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>138</v>
+        <v>181</v>
       </c>
       <c r="C96">
         <v>0</v>
       </c>
       <c r="D96">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E96" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="F96" t="s">
         <v>6</v>
@@ -2936,16 +2948,16 @@
         <v>97</v>
       </c>
       <c r="B97" t="s">
-        <v>182</v>
+        <v>127</v>
       </c>
       <c r="C97">
         <v>0</v>
       </c>
       <c r="D97">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E97" t="s">
-        <v>184</v>
+        <v>128</v>
       </c>
       <c r="F97" t="s">
         <v>6</v>
@@ -2956,16 +2968,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>187</v>
+        <v>138</v>
       </c>
       <c r="C98">
         <v>0</v>
       </c>
       <c r="D98">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E98" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F98" t="s">
         <v>6</v>
@@ -2976,16 +2988,16 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="C99">
         <v>0</v>
       </c>
       <c r="D99">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E99" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="F99" t="s">
         <v>6</v>
@@ -2996,13 +3008,13 @@
         <v>97</v>
       </c>
       <c r="B100" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="C100">
         <v>0</v>
       </c>
       <c r="D100">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E100" t="s">
         <v>140</v>
@@ -3016,13 +3028,13 @@
         <v>97</v>
       </c>
       <c r="B101" t="s">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="C101">
         <v>0</v>
       </c>
       <c r="D101">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E101" t="s">
         <v>140</v>
@@ -3036,16 +3048,16 @@
         <v>97</v>
       </c>
       <c r="B102" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="C102">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D102">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E102" t="s">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="F102" t="s">
         <v>6</v>
@@ -3056,16 +3068,16 @@
         <v>97</v>
       </c>
       <c r="B103" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="C103">
         <v>0</v>
       </c>
       <c r="D103">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E103" t="s">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="F103" t="s">
         <v>6</v>
@@ -3076,13 +3088,13 @@
         <v>97</v>
       </c>
       <c r="B104" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E104" t="s">
         <v>178</v>
@@ -3096,18 +3108,58 @@
         <v>97</v>
       </c>
       <c r="B105" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="C105">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E105" t="s">
         <v>178</v>
       </c>
       <c r="F105" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>97</v>
+      </c>
+      <c r="B106" t="s">
+        <v>190</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+      <c r="D106">
+        <v>1</v>
+      </c>
+      <c r="E106" t="s">
+        <v>178</v>
+      </c>
+      <c r="F106" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>97</v>
+      </c>
+      <c r="B107" t="s">
+        <v>191</v>
+      </c>
+      <c r="C107">
+        <v>3</v>
+      </c>
+      <c r="D107">
+        <v>5</v>
+      </c>
+      <c r="E107" t="s">
+        <v>178</v>
+      </c>
+      <c r="F107" t="s">
         <v>6</v>
       </c>
     </row>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE2F19F-A4D6-41C6-8A63-EA535F8F3EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E32C50B3-B0DC-4268-B05B-17663784F539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$84</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="208">
   <si>
     <t>Item</t>
   </si>
@@ -641,6 +641,12 @@
   </si>
   <si>
     <t>Aloo Pakodi.jpg</t>
+  </si>
+  <si>
+    <t>Bread Pakora</t>
+  </si>
+  <si>
+    <t>Bread Pakora.jpg</t>
   </si>
 </sst>
 </file>
@@ -1013,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -1908,16 +1914,16 @@
         <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E45" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="F45" t="s">
         <v>6</v>
@@ -1928,16 +1934,16 @@
         <v>99</v>
       </c>
       <c r="B46" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
         <v>30</v>
       </c>
-      <c r="D46">
-        <v>50</v>
-      </c>
       <c r="E46" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F46" t="s">
         <v>6</v>
@@ -1948,16 +1954,16 @@
         <v>99</v>
       </c>
       <c r="B47" t="s">
-        <v>56</v>
+        <v>204</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D47">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E47" t="s">
-        <v>57</v>
+        <v>205</v>
       </c>
       <c r="F47" t="s">
         <v>6</v>
@@ -1968,16 +1974,16 @@
         <v>99</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C48">
         <v>0</v>
       </c>
       <c r="D48">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E48" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F48" t="s">
         <v>6</v>
@@ -1988,16 +1994,16 @@
         <v>99</v>
       </c>
       <c r="B49" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F49" t="s">
         <v>6</v>
@@ -2008,16 +2014,16 @@
         <v>99</v>
       </c>
       <c r="B50" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C50">
         <v>0</v>
       </c>
       <c r="D50">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E50" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F50" t="s">
         <v>6</v>
@@ -2028,16 +2034,16 @@
         <v>99</v>
       </c>
       <c r="B51" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E51" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F51" t="s">
         <v>6</v>
@@ -2048,16 +2054,16 @@
         <v>99</v>
       </c>
       <c r="B52" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E52" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F52" t="s">
         <v>6</v>
@@ -2068,16 +2074,16 @@
         <v>99</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E53" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F53" t="s">
         <v>6</v>
@@ -2088,7 +2094,7 @@
         <v>99</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -2097,7 +2103,7 @@
         <v>10</v>
       </c>
       <c r="E54" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F54" t="s">
         <v>6</v>
@@ -2108,16 +2114,16 @@
         <v>99</v>
       </c>
       <c r="B55" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E55" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F55" t="s">
         <v>6</v>
@@ -2128,16 +2134,16 @@
         <v>99</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E56" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F56" t="s">
         <v>6</v>
@@ -2148,16 +2154,16 @@
         <v>99</v>
       </c>
       <c r="B57" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E57" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F57" t="s">
         <v>6</v>
@@ -2168,16 +2174,16 @@
         <v>99</v>
       </c>
       <c r="B58" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="E58" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="F58" t="s">
         <v>6</v>
@@ -2188,16 +2194,16 @@
         <v>99</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="E59" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="F59" t="s">
         <v>6</v>
@@ -2208,16 +2214,16 @@
         <v>99</v>
       </c>
       <c r="B60" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E60" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F60" t="s">
         <v>6</v>
@@ -2228,16 +2234,16 @@
         <v>99</v>
       </c>
       <c r="B61" t="s">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E61" t="s">
-        <v>189</v>
+        <v>80</v>
       </c>
       <c r="F61" t="s">
         <v>6</v>
@@ -2248,16 +2254,16 @@
         <v>99</v>
       </c>
       <c r="B62" t="s">
-        <v>105</v>
+        <v>188</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="E62" t="s">
-        <v>104</v>
+        <v>189</v>
       </c>
       <c r="F62" t="s">
         <v>6</v>
@@ -2268,16 +2274,16 @@
         <v>99</v>
       </c>
       <c r="B63" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E63" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F63" t="s">
         <v>6</v>
@@ -2288,16 +2294,16 @@
         <v>99</v>
       </c>
       <c r="B64" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E64" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F64" t="s">
         <v>6</v>
@@ -2308,7 +2314,7 @@
         <v>99</v>
       </c>
       <c r="B65" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -2317,7 +2323,7 @@
         <v>52</v>
       </c>
       <c r="E65" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F65" t="s">
         <v>6</v>
@@ -2328,16 +2334,16 @@
         <v>99</v>
       </c>
       <c r="B66" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E66" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F66" t="s">
         <v>6</v>
@@ -2348,16 +2354,16 @@
         <v>99</v>
       </c>
       <c r="B67" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E67" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="F67" t="s">
         <v>6</v>
@@ -2368,16 +2374,16 @@
         <v>99</v>
       </c>
       <c r="B68" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
       <c r="D68">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E68" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F68" t="s">
         <v>6</v>
@@ -2388,7 +2394,7 @@
         <v>99</v>
       </c>
       <c r="B69" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -2397,7 +2403,7 @@
         <v>10</v>
       </c>
       <c r="E69" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F69" t="s">
         <v>6</v>
@@ -2408,16 +2414,16 @@
         <v>99</v>
       </c>
       <c r="B70" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E70" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F70" t="s">
         <v>6</v>
@@ -2428,16 +2434,16 @@
         <v>99</v>
       </c>
       <c r="B71" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E71" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="F71" t="s">
         <v>6</v>
@@ -2448,16 +2454,16 @@
         <v>99</v>
       </c>
       <c r="B72" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E72" t="s">
-        <v>174</v>
+        <v>120</v>
       </c>
       <c r="F72" t="s">
         <v>6</v>
@@ -2468,16 +2474,16 @@
         <v>99</v>
       </c>
       <c r="B73" t="s">
-        <v>123</v>
+        <v>170</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E73" t="s">
-        <v>124</v>
+        <v>174</v>
       </c>
       <c r="F73" t="s">
         <v>6</v>
@@ -2488,16 +2494,16 @@
         <v>99</v>
       </c>
       <c r="B74" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E74" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="F74" t="s">
         <v>6</v>
@@ -2505,19 +2511,19 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B75" t="s">
-        <v>202</v>
+        <v>112</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>203</v>
+        <v>113</v>
       </c>
       <c r="F75" t="s">
         <v>6</v>
@@ -2528,16 +2534,16 @@
         <v>97</v>
       </c>
       <c r="B76" t="s">
-        <v>81</v>
+        <v>202</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E76" t="s">
-        <v>82</v>
+        <v>203</v>
       </c>
       <c r="F76" t="s">
         <v>6</v>
@@ -2548,7 +2554,7 @@
         <v>97</v>
       </c>
       <c r="B77" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2557,7 +2563,7 @@
         <v>10</v>
       </c>
       <c r="E77" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F77" t="s">
         <v>6</v>
@@ -2568,7 +2574,7 @@
         <v>97</v>
       </c>
       <c r="B78" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2577,7 +2583,7 @@
         <v>10</v>
       </c>
       <c r="E78" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F78" t="s">
         <v>6</v>
@@ -2588,7 +2594,7 @@
         <v>97</v>
       </c>
       <c r="B79" t="s">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2597,7 +2603,7 @@
         <v>10</v>
       </c>
       <c r="E79" t="s">
-        <v>172</v>
+        <v>86</v>
       </c>
       <c r="F79" t="s">
         <v>6</v>
@@ -2608,16 +2614,16 @@
         <v>97</v>
       </c>
       <c r="B80" t="s">
-        <v>87</v>
+        <v>171</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E80" t="s">
-        <v>88</v>
+        <v>172</v>
       </c>
       <c r="F80" t="s">
         <v>6</v>
@@ -2628,7 +2634,7 @@
         <v>97</v>
       </c>
       <c r="B81" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2637,7 +2643,7 @@
         <v>20</v>
       </c>
       <c r="E81" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F81" t="s">
         <v>6</v>
@@ -2648,7 +2654,7 @@
         <v>97</v>
       </c>
       <c r="B82" t="s">
-        <v>183</v>
+        <v>89</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2657,7 +2663,7 @@
         <v>20</v>
       </c>
       <c r="E82" t="s">
-        <v>184</v>
+        <v>90</v>
       </c>
       <c r="F82" t="s">
         <v>6</v>
@@ -2668,7 +2674,7 @@
         <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>95</v>
+        <v>183</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2677,7 +2683,7 @@
         <v>20</v>
       </c>
       <c r="E83" t="s">
-        <v>96</v>
+        <v>184</v>
       </c>
       <c r="F83" t="s">
         <v>6</v>
@@ -2688,7 +2694,7 @@
         <v>97</v>
       </c>
       <c r="B84" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2697,7 +2703,7 @@
         <v>20</v>
       </c>
       <c r="E84" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F84" t="s">
         <v>6</v>
@@ -2708,7 +2714,7 @@
         <v>97</v>
       </c>
       <c r="B85" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2717,7 +2723,7 @@
         <v>20</v>
       </c>
       <c r="E85" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F85" t="s">
         <v>6</v>
@@ -2728,7 +2734,7 @@
         <v>97</v>
       </c>
       <c r="B86" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2737,7 +2743,7 @@
         <v>20</v>
       </c>
       <c r="E86" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="F86" t="s">
         <v>6</v>
@@ -2748,16 +2754,16 @@
         <v>97</v>
       </c>
       <c r="B87" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="C87">
         <v>0</v>
       </c>
       <c r="D87">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E87" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="F87" t="s">
         <v>6</v>
@@ -2768,16 +2774,16 @@
         <v>97</v>
       </c>
       <c r="B88" t="s">
-        <v>200</v>
+        <v>152</v>
       </c>
       <c r="C88">
         <v>0</v>
       </c>
       <c r="D88">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E88" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F88" t="s">
         <v>6</v>
@@ -2788,16 +2794,16 @@
         <v>97</v>
       </c>
       <c r="B89" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E89" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F89" t="s">
         <v>6</v>
@@ -2808,16 +2814,16 @@
         <v>97</v>
       </c>
       <c r="B90" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="E90" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="F90" t="s">
         <v>6</v>
@@ -2828,16 +2834,16 @@
         <v>97</v>
       </c>
       <c r="B91" t="s">
-        <v>169</v>
+        <v>125</v>
       </c>
       <c r="C91">
         <v>0</v>
       </c>
       <c r="D91">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E91" t="s">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="F91" t="s">
         <v>6</v>
@@ -2848,16 +2854,16 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C92">
         <v>0</v>
       </c>
       <c r="D92">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="E92" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F92" t="s">
         <v>6</v>
@@ -2868,16 +2874,16 @@
         <v>97</v>
       </c>
       <c r="B93" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="E93" t="s">
-        <v>93</v>
+        <v>176</v>
       </c>
       <c r="F93" t="s">
         <v>6</v>
@@ -2888,16 +2894,16 @@
         <v>97</v>
       </c>
       <c r="B94" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="C94">
         <v>0</v>
       </c>
       <c r="D94">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E94" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="F94" t="s">
         <v>6</v>
@@ -2908,16 +2914,16 @@
         <v>97</v>
       </c>
       <c r="B95" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="C95">
         <v>0</v>
       </c>
       <c r="D95">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E95" t="s">
-        <v>184</v>
+        <v>128</v>
       </c>
       <c r="F95" t="s">
         <v>6</v>
@@ -2928,13 +2934,13 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C96">
         <v>0</v>
       </c>
       <c r="D96">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E96" t="s">
         <v>184</v>
@@ -2948,16 +2954,16 @@
         <v>97</v>
       </c>
       <c r="B97" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="C97">
         <v>0</v>
       </c>
       <c r="D97">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="E97" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="F97" t="s">
         <v>6</v>
@@ -2968,16 +2974,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="C98">
         <v>0</v>
       </c>
       <c r="D98">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E98" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="F98" t="s">
         <v>6</v>
@@ -2988,7 +2994,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>182</v>
+        <v>138</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -2997,7 +3003,7 @@
         <v>100</v>
       </c>
       <c r="E99" t="s">
-        <v>184</v>
+        <v>141</v>
       </c>
       <c r="F99" t="s">
         <v>6</v>
@@ -3008,16 +3014,16 @@
         <v>97</v>
       </c>
       <c r="B100" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C100">
         <v>0</v>
       </c>
       <c r="D100">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E100" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="F100" t="s">
         <v>6</v>
@@ -3028,13 +3034,13 @@
         <v>97</v>
       </c>
       <c r="B101" t="s">
-        <v>139</v>
+        <v>187</v>
       </c>
       <c r="C101">
         <v>0</v>
       </c>
       <c r="D101">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E101" t="s">
         <v>140</v>
@@ -3048,13 +3054,13 @@
         <v>97</v>
       </c>
       <c r="B102" t="s">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="C102">
         <v>0</v>
       </c>
       <c r="D102">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E102" t="s">
         <v>140</v>
@@ -3068,13 +3074,13 @@
         <v>97</v>
       </c>
       <c r="B103" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C103">
         <v>0</v>
       </c>
       <c r="D103">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E103" t="s">
         <v>140</v>
@@ -3088,16 +3094,16 @@
         <v>97</v>
       </c>
       <c r="B104" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="C104">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E104" t="s">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="F104" t="s">
         <v>6</v>
@@ -3108,13 +3114,13 @@
         <v>97</v>
       </c>
       <c r="B105" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D105">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E105" t="s">
         <v>178</v>
@@ -3128,13 +3134,13 @@
         <v>97</v>
       </c>
       <c r="B106" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="C106">
         <v>0</v>
       </c>
       <c r="D106">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E106" t="s">
         <v>178</v>
@@ -3148,18 +3154,38 @@
         <v>97</v>
       </c>
       <c r="B107" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C107">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E107" t="s">
         <v>178</v>
       </c>
       <c r="F107" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>97</v>
+      </c>
+      <c r="B108" t="s">
+        <v>191</v>
+      </c>
+      <c r="C108">
+        <v>3</v>
+      </c>
+      <c r="D108">
+        <v>5</v>
+      </c>
+      <c r="E108" t="s">
+        <v>178</v>
+      </c>
+      <c r="F108" t="s">
         <v>6</v>
       </c>
     </row>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E32C50B3-B0DC-4268-B05B-17663784F539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4282D81C-1055-448C-A267-85B4ECAFE783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1720,7 +1720,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E35" t="s">
         <v>44</v>
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E36" t="s">
         <v>46</v>
@@ -1840,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="E41" t="s">
         <v>48</v>
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="E42" t="s">
         <v>52</v>
